--- a/Grupo/UOcc_Grupo.xlsx
+++ b/Grupo/UOcc_Grupo.xlsx
@@ -458,16 +458,16 @@
         <v>5</v>
       </c>
       <c r="B2" s="2">
-        <v>50.37352578580168</v>
+        <v>50.37352578580169</v>
       </c>
       <c r="C2" s="2">
-        <v>115.8320944375873</v>
+        <v>115.833185879141</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>6</v>
       </c>
       <c r="E2" s="2">
-        <v>58.34870995975221</v>
+        <v>58.34925975734469</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -492,7 +492,7 @@
         <v>8</v>
       </c>
       <c r="B4" s="2">
-        <v>3.356111038578651</v>
+        <v>3.35611103857865</v>
       </c>
       <c r="C4" s="2">
         <v>105.324147891709</v>
@@ -577,7 +577,7 @@
         <v>13</v>
       </c>
       <c r="B9" s="2">
-        <v>0.8450214000591739</v>
+        <v>0.845021400059174</v>
       </c>
       <c r="C9" s="2">
         <v>119.3188732743229</v>
@@ -603,7 +603,7 @@
         <v>6</v>
       </c>
       <c r="E10" s="2">
-        <v>0.5193151654974559</v>
+        <v>0.5193151654974562</v>
       </c>
     </row>
     <row r="11" spans="1:5">
